--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MISSISSIPPI_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MISSISSIPPI_2020.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C67">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C74">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C103">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C135">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C139">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C146">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C191">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C294">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C310">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C377">
